--- a/artfynd/A 55503-2022 artfynd.xlsx
+++ b/artfynd/A 55503-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121378398</v>
       </c>
       <c r="B2" t="n">
-        <v>97988</v>
+        <v>97998</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 55503-2022 artfynd.xlsx
+++ b/artfynd/A 55503-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121378398</v>
       </c>
       <c r="B2" t="n">
-        <v>97998</v>
+        <v>98011</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 55503-2022 artfynd.xlsx
+++ b/artfynd/A 55503-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121378398</v>
       </c>
       <c r="B2" t="n">
-        <v>98011</v>
+        <v>98012</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 55503-2022 artfynd.xlsx
+++ b/artfynd/A 55503-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121378398</v>
       </c>
       <c r="B2" t="n">
-        <v>98012</v>
+        <v>98015</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 55503-2022 artfynd.xlsx
+++ b/artfynd/A 55503-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121378398</v>
       </c>
       <c r="B2" t="n">
-        <v>98015</v>
+        <v>98021</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 55503-2022 artfynd.xlsx
+++ b/artfynd/A 55503-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121378398</v>
       </c>
       <c r="B2" t="n">
-        <v>98021</v>
+        <v>98022</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 55503-2022 artfynd.xlsx
+++ b/artfynd/A 55503-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121378398</v>
       </c>
       <c r="B2" t="n">
-        <v>98022</v>
+        <v>98030</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
